--- a/FLORES DE ESTRADA/Septiembre/PRORRATEO Septiembre Estrada.xlsx
+++ b/FLORES DE ESTRADA/Septiembre/PRORRATEO Septiembre Estrada.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B4CB4E-6D94-4152-90DD-148E534925E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABE1168-0E51-41B6-902E-B3CDD74108EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -271,10 +271,7 @@
     <t xml:space="preserve">Antonella </t>
   </si>
   <si>
-    <t>Federico</t>
-  </si>
-  <si>
-    <t>EXPENSAS - VENCIMIENTO 15/09  LIQUIDACION : AGOSTO</t>
+    <t>EXPENSAS - VENCIMIENTO 15/09  LIQUIDACION : SEPTIEMBRE</t>
   </si>
 </sst>
 </file>
@@ -282,11 +279,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -608,21 +605,21 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -636,31 +633,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -675,58 +672,59 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1107,22 +1105,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="72"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
@@ -1155,13 +1153,13 @@
       <c r="I4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="67">
+      <c r="J4" s="68">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="69"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -1192,7 +1190,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="50">
-        <v>1302201.98</v>
+        <v>1400000</v>
       </c>
       <c r="D7" s="53"/>
       <c r="F7" s="7"/>
@@ -1206,9 +1204,7 @@
       <c r="B8" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="29">
-        <v>700000</v>
-      </c>
+      <c r="C8" s="29"/>
       <c r="D8" s="29"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -1310,15 +1306,15 @@
       </c>
       <c r="L11" s="5">
         <f>C7*E11/100</f>
-        <v>63807.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
       <c r="M11" s="5">
         <f>C8*E11/100</f>
-        <v>34300.000000000007</v>
+        <v>0</v>
       </c>
       <c r="N11" s="44">
         <f>K11+L11+M11</f>
-        <v>98107.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1338,35 +1334,35 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>800086.0071855844</v>
+        <v>948379.2328399159</v>
       </c>
       <c r="G12" s="62"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>800086.0071855844</v>
+        <v>948379.2328399159</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>70407.568632331429</v>
+        <v>83457.37248991261</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>870493.57581791584</v>
+        <v>1031836.6053298286</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
-        <v>50655.657021999999</v>
+        <v>54460</v>
       </c>
       <c r="M12" s="5">
         <f>C8*E12/100</f>
-        <v>27230</v>
+        <v>0</v>
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>948379.2328399159</v>
+        <v>1086296.6053298286</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1409,15 +1405,19 @@
       </c>
       <c r="L13" s="5">
         <f>C7*E13/100</f>
-        <v>52088.0792</v>
+        <v>56000</v>
       </c>
       <c r="M13" s="5">
         <f>C8*E13/100</f>
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="N13" s="44">
         <f>K13+L13+M13</f>
-        <v>80088.079200000007</v>
+        <v>56000</v>
+      </c>
+      <c r="P13" s="66">
+        <f>G13+G30</f>
+        <v>103715.06256400001</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1460,15 +1460,15 @@
       </c>
       <c r="L14" s="5">
         <f>C7*E14/100</f>
-        <v>63807.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
       <c r="M14" s="5">
         <f>C8*E14/100</f>
-        <v>34300.000000000007</v>
+        <v>0</v>
       </c>
       <c r="N14" s="44">
         <f t="shared" ref="N14:N24" si="3">K14+L14+M14</f>
-        <v>98107.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1488,11 +1488,11 @@
         <v>3.89</v>
       </c>
       <c r="F15" s="5">
-        <v>107511.897022</v>
+        <v>77885.657021999999</v>
       </c>
       <c r="G15" s="62">
         <f>F15</f>
-        <v>107511.897022</v>
+        <v>77885.657021999999</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
@@ -1511,15 +1511,15 @@
       </c>
       <c r="L15" s="5">
         <f>C7*E15/100</f>
-        <v>50655.657021999999</v>
+        <v>54460</v>
       </c>
       <c r="M15" s="5">
         <f>C8*E15/100</f>
-        <v>27230</v>
+        <v>0</v>
       </c>
       <c r="N15" s="44">
         <f>K15+L15+M15</f>
-        <v>77885.657021999999</v>
+        <v>54460</v>
       </c>
       <c r="P15" s="59"/>
     </row>
@@ -1540,37 +1540,37 @@
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>80088.079200000007</v>
+        <v>110552.1653696</v>
       </c>
       <c r="G16" s="62">
         <v>52088</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>28000.079200000007</v>
+        <v>58464.165369599999</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>2464.006969600001</v>
+        <v>5144.8465525248002</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>30464.086169600007</v>
+        <v>63609.011922124802</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
-        <v>52088.0792</v>
+        <v>56000</v>
       </c>
       <c r="M16" s="5">
         <f>C8*E16/100</f>
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>110552.1653696</v>
+        <v>119609.0119221248</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1613,15 +1613,15 @@
       </c>
       <c r="L17" s="5">
         <f>C7*E17/100</f>
-        <v>63807.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
       <c r="M17" s="5">
         <f>C8*E17/100</f>
-        <v>34300.000000000007</v>
+        <v>0</v>
       </c>
       <c r="N17" s="44">
         <f>K17+L17+M17</f>
-        <v>98107.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -1662,15 +1662,15 @@
       </c>
       <c r="L18" s="5">
         <f>C7*E18/100</f>
-        <v>50655.657021999999</v>
+        <v>54460</v>
       </c>
       <c r="M18" s="5">
         <f>C8*E18/100</f>
-        <v>27230</v>
+        <v>0</v>
       </c>
       <c r="N18" s="44">
         <f t="shared" si="3"/>
-        <v>77885.657021999999</v>
+        <v>54460</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -1713,15 +1713,15 @@
       </c>
       <c r="L19" s="5">
         <f>C7*E19/100</f>
-        <v>52088.0792</v>
+        <v>56000</v>
       </c>
       <c r="M19" s="5">
         <f>C8*E19/100</f>
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="N19" s="44">
         <f t="shared" si="3"/>
-        <v>80088.079200000007</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -1739,11 +1739,11 @@
         <v>12.66</v>
       </c>
       <c r="F20" s="5">
-        <v>248716.34515478404</v>
+        <v>253478.77066800001</v>
       </c>
       <c r="G20" s="62">
         <f>F20</f>
-        <v>248716.34515478404</v>
+        <v>253478.77066800001</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
@@ -1762,15 +1762,15 @@
       </c>
       <c r="L20" s="5">
         <f>C7*E20/100</f>
-        <v>164858.77066800001</v>
+        <v>177240</v>
       </c>
       <c r="M20" s="5">
         <f>C8*E20/100</f>
-        <v>88620</v>
+        <v>0</v>
       </c>
       <c r="N20" s="44">
         <f>K20+L20+M20</f>
-        <v>253478.77066800001</v>
+        <v>177240</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -1813,15 +1813,15 @@
       </c>
       <c r="L21" s="5">
         <f>C7*E21/100</f>
-        <v>100920.65345000001</v>
+        <v>108500</v>
       </c>
       <c r="M21" s="5">
         <f>C8*E21/100</f>
-        <v>54250</v>
+        <v>0</v>
       </c>
       <c r="N21" s="44">
         <f t="shared" si="3"/>
-        <v>155170.65345000001</v>
+        <v>108500</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1839,35 +1839,38 @@
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>313962.88984142395</v>
-      </c>
-      <c r="G22" s="62"/>
+        <v>491956.99284546921</v>
+      </c>
+      <c r="G22" s="62">
+        <f>F22</f>
+        <v>491956.99284546921</v>
+      </c>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>313962.88984142395</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>27628.734306045309</v>
+        <v>0</v>
       </c>
       <c r="K22" s="44">
         <f t="shared" ref="K22:K24" si="6">H22+J22+I22</f>
-        <v>341591.62414746924</v>
+        <v>0</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
-        <v>97795.368697999991</v>
+        <v>105140</v>
       </c>
       <c r="M22" s="5">
         <f>C8*E22/100</f>
-        <v>52570</v>
+        <v>0</v>
       </c>
       <c r="N22" s="44">
         <f t="shared" si="3"/>
-        <v>491956.99284546921</v>
+        <v>105140</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1885,35 +1888,37 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>424954.42361230979</v>
-      </c>
-      <c r="G23" s="62"/>
+        <v>551448.40100019309</v>
+      </c>
+      <c r="G23" s="62">
+        <v>326017</v>
+      </c>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>424954.42361230979</v>
+        <v>225431.40100019309</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>37395.989277883265</v>
+        <v>19837.963288016992</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>462350.41289019305</v>
+        <v>245269.36428821008</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
-        <v>57947.988109999998</v>
+        <v>62300</v>
       </c>
       <c r="M23" s="5">
         <f>C8*E23/100</f>
-        <v>31150</v>
+        <v>0</v>
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>551448.40100019309</v>
+        <v>307569.36428821005</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1954,15 +1959,15 @@
       </c>
       <c r="L24" s="5">
         <f>C7*E24/100</f>
-        <v>80345.862166000006</v>
+        <v>86380</v>
       </c>
       <c r="M24" s="5">
         <f>C8*E24/100</f>
-        <v>43190</v>
+        <v>0</v>
       </c>
       <c r="N24" s="44">
         <f t="shared" si="3"/>
-        <v>123535.86216600001</v>
+        <v>86380</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -1982,37 +1987,37 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>428598.78514700249</v>
+        <v>492365.95434993866</v>
       </c>
       <c r="G25" s="62">
         <v>57949</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>370649.78514700249</v>
+        <v>434416.95434993866</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>32617.181092936222</v>
+        <v>38228.691982794604</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>403266.96623993869</v>
+        <v>472645.64633273327</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
-        <v>57948.988109999998</v>
+        <v>62301</v>
       </c>
       <c r="M25" s="5">
         <f>C8*E25/100</f>
-        <v>31150</v>
+        <v>0</v>
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>492365.95434993866</v>
+        <v>534946.64633273333</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2032,37 +2037,38 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>1229173.3314329986</v>
+        <v>1348192.0105611025</v>
       </c>
       <c r="G26" s="62">
-        <v>159147</v>
+        <f>300000-132973</f>
+        <v>167027</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>1070026.3314329986</v>
+        <v>1181165.0105611025</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>94162.317166103894</v>
+        <v>103942.52092937703</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>1164188.6485991026</v>
+        <v>1285107.5314904796</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
-        <v>119673.36196199998</v>
+        <v>128661</v>
       </c>
       <c r="M26" s="5">
         <f>C8*E26/100</f>
-        <v>64330</v>
+        <v>0</v>
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>1348192.0105611025</v>
+        <v>1413768.5314904796</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2105,15 +2111,15 @@
       </c>
       <c r="L27" s="5">
         <f>C7*E27/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M27" s="5">
         <f>C8*E27/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N27" s="44">
         <f>K27+L27+M27</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2131,35 +2137,35 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>97181.948068334197</v>
+        <v>129360.94286234761</v>
       </c>
       <c r="G28" s="62"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>97181.948068334197</v>
+        <v>129360.94286234761</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>8552.0114300134101</v>
+        <v>11383.762971886592</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="7"/>
-        <v>105733.95949834761</v>
+        <v>140744.70583423419</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M28" s="5">
         <f>C8*E28/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>129360.94286234761</v>
+        <v>157265.70583423419</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2177,35 +2183,35 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>97181.948068334197</v>
+        <v>129360.94286234761</v>
       </c>
       <c r="G29" s="62"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>97181.948068334197</v>
+        <v>129360.94286234761</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>8552.0114300134101</v>
+        <v>11383.762971886592</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="7"/>
-        <v>105733.95949834761</v>
+        <v>140744.70583423419</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M29" s="5">
         <f>C8*E29/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>129360.94286234761</v>
+        <v>157265.70583423419</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2246,15 +2252,15 @@
       </c>
       <c r="L30" s="5">
         <f>C7*E30/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M30" s="5">
         <f>C8*E30/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N30" s="44">
         <f>K30+L30+M30</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2295,15 +2301,15 @@
       </c>
       <c r="L31" s="5">
         <f>C7*E31/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M31" s="5">
         <f>C8*E31/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N31" s="44">
         <f>K31+L31+M31</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2344,15 +2350,15 @@
       </c>
       <c r="L32" s="5">
         <f>C7*E32/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M32" s="5">
         <f>C8*E32/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N32" s="44">
         <f t="shared" si="8"/>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2393,15 +2399,15 @@
       </c>
       <c r="L33" s="5">
         <f>C7*E33/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M33" s="5">
         <f>C8*E33/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N33" s="44">
         <f>K33+L33+M33</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
       <c r="O33" s="59"/>
     </row>
@@ -2415,50 +2421,51 @@
       <c r="C34" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="55" t="s">
-        <v>81</v>
-      </c>
+      <c r="D34" s="55"/>
       <c r="E34" s="1">
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>49333.141264031998</v>
-      </c>
-      <c r="G34" s="62"/>
+        <v>77301.441059266814</v>
+      </c>
+      <c r="G34" s="62">
+        <f>F34</f>
+        <v>77301.441059266814</v>
+      </c>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
-        <v>49333.141264031998</v>
+        <v>0</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>4341.3164312348163</v>
+        <v>0</v>
       </c>
       <c r="K34" s="44">
         <f t="shared" si="7"/>
-        <v>53674.457695266814</v>
+        <v>0</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
-        <v>15366.983364</v>
+        <v>16521</v>
       </c>
       <c r="M34" s="5">
         <f>C8*E34/100</f>
-        <v>8260</v>
+        <v>0</v>
       </c>
       <c r="N34" s="44">
         <f t="shared" si="8"/>
-        <v>77301.441059266814</v>
+        <v>16521</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
       <c r="D35" s="52"/>
       <c r="E35" s="45">
         <f>SUM(E11:E34)</f>
@@ -2466,15 +2473,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>4806015.734914802</v>
+        <v>5539509.4503581822</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1554639.1810947841</v>
+        <v>2432930.8005127362</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>3251376.5538200201</v>
+        <v>3106578.6498454455</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2482,20 +2489,20 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>286121.13673616177</v>
+        <v>273378.92118639924</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
         <f>SUM(L11:L34)</f>
-        <v>1302081.7598019997</v>
+        <v>1399870</v>
       </c>
       <c r="M35" s="51">
         <f>SUM(M11:M34)</f>
-        <v>699930</v>
+        <v>0</v>
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>5539509.4503581822</v>
+        <v>4779827.5710318442</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3271,11 +3278,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A29" s="72" t="s">
+      <c r="A29" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
       <c r="D29" s="27">
         <f>SUM(D5:D28)</f>
         <v>99.990000000000066</v>
